--- a/htr-update-fr-medication/ig/StructureDefinition-fr-condition-document.xlsx
+++ b/htr-update-fr-medication/ig/StructureDefinition-fr-condition-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-27T08:28:14+00:00</t>
+    <t>2026-09-04T09:33:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -6424,7 +6424,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="41" hidden="true">
+    <row r="41">
       <c r="A41" t="s" s="2">
         <v>312</v>
       </c>
@@ -6445,7 +6445,7 @@
         <v>91</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>79</v>
